--- a/RSVP_Guest_List_import.xlsx
+++ b/RSVP_Guest_List_import.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://syngenta-my.sharepoint.com/personal/alejandro_lajnis_syngenta_com/Documents/Ale Personal/IA/RSVP app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{0669B2AD-BB49-463B-A45C-FF5CB10682AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5067DD5A-2DE2-4FCA-8136-9E4D53296BFA}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{0669B2AD-BB49-463B-A45C-FF5CB10682AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5ED5440B-7037-424B-B948-B5E743DEBFD4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,26 +33,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Guest_Count</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
   <si>
     <t>Email</t>
   </si>
   <si>
-    <t>Phone</t>
-  </si>
-  <si>
-    <t>Dietary</t>
-  </si>
-  <si>
-    <t>Table</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -95,16 +80,43 @@
     <t>taylor4@era.com</t>
   </si>
   <si>
-    <t>Brad</t>
-  </si>
-  <si>
-    <t>Jlo</t>
-  </si>
-  <si>
-    <t>Leo</t>
-  </si>
-  <si>
-    <t>Taylor</t>
+    <t>Apellido</t>
+  </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Cantidad de invitados</t>
+  </si>
+  <si>
+    <t>Tel</t>
+  </si>
+  <si>
+    <t>Dieta?</t>
+  </si>
+  <si>
+    <t>Mesa</t>
+  </si>
+  <si>
+    <t>Lajnis</t>
+  </si>
+  <si>
+    <t>Ale</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>Fauda</t>
+  </si>
+  <si>
+    <t>Sofia</t>
+  </si>
+  <si>
+    <t>Lerner</t>
+  </si>
+  <si>
+    <t>Alicia</t>
   </si>
 </sst>
 </file>
@@ -498,138 +510,153 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>21</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
         <v>7</v>
       </c>
+      <c r="G4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5">
         <v>3</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>10</v>
       </c>
       <c r="G5" t="s">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="H5" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{217FEA78-9780-4BBB-A41B-71E299723666}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{A2831DCE-E735-4E3D-86D8-9B01A30514A5}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{21AE655A-7693-4384-ACCE-54991CF75E71}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{B66C0F70-DAA6-40FF-87FA-9D6C9F814BCE}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{217FEA78-9780-4BBB-A41B-71E299723666}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{A2831DCE-E735-4E3D-86D8-9B01A30514A5}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{21AE655A-7693-4384-ACCE-54991CF75E71}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{B66C0F70-DAA6-40FF-87FA-9D6C9F814BCE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1 B2 B5 D2:G2 B3 D3:E3 B4 D4:E4 D5:E5 B1:G1" numberStoredAsText="1"/>
+    <ignoredError sqref="C2 C5 E2:H2 C3 E3:F3 C4 E4:F4 E5:F5 D1 H1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/RSVP_Guest_List_import.xlsx
+++ b/RSVP_Guest_List_import.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://syngenta-my.sharepoint.com/personal/alejandro_lajnis_syngenta_com/Documents/Ale Personal/IA/RSVP app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{0669B2AD-BB49-463B-A45C-FF5CB10682AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5ED5440B-7037-424B-B948-B5E743DEBFD4}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="8_{0669B2AD-BB49-463B-A45C-FF5CB10682AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82CDEF07-9FB4-4AB1-96A2-5391036321DF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -123,7 +123,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -145,13 +145,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -167,9 +181,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -186,6 +201,89 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1714500" cy="781240"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2F73242-AB8F-548F-1E00-6EBBD5EB7B08}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5511800" y="44450"/>
+          <a:ext cx="1714500" cy="781240"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Completar Obligatoriamente Apellido, Nombre</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> y cantidad de invitados</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -513,17 +611,17 @@
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.9140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D1" t="s">
@@ -658,6 +756,7 @@
   <ignoredErrors>
     <ignoredError sqref="C2 C5 E2:H2 C3 E3:F3 C4 E4:F4 E5:F5 D1 H1" numberStoredAsText="1"/>
   </ignoredErrors>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
 

--- a/RSVP_Guest_List_import.xlsx
+++ b/RSVP_Guest_List_import.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://syngenta-my.sharepoint.com/personal/alejandro_lajnis_syngenta_com/Documents/Ale Personal/IA/RSVP app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{0669B2AD-BB49-463B-A45C-FF5CB10682AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82CDEF07-9FB4-4AB1-96A2-5391036321DF}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{0669B2AD-BB49-463B-A45C-FF5CB10682AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD8AD655-87C5-47BD-9AF7-BC2A03673668}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guests (Alpha)" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
   <si>
     <t>Email</t>
   </si>
@@ -117,6 +118,27 @@
   </si>
   <si>
     <t>Alicia</t>
+  </si>
+  <si>
+    <t>edad</t>
+  </si>
+  <si>
+    <t>Adulto</t>
+  </si>
+  <si>
+    <t>Niño</t>
+  </si>
+  <si>
+    <t>Teen</t>
+  </si>
+  <si>
+    <t>Bebé</t>
+  </si>
+  <si>
+    <t>Sueyro</t>
+  </si>
+  <si>
+    <t>Matias</t>
   </si>
 </sst>
 </file>
@@ -207,10 +229,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1714500" cy="781240"/>
     <xdr:sp macro="" textlink="">
@@ -226,7 +248,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5511800" y="44450"/>
+          <a:off x="6896100" y="57150"/>
           <a:ext cx="1714500" cy="781240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -608,13 +630,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="18.9140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>15</v>
       </c>
@@ -639,8 +661,11 @@
       <c r="H1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -665,8 +690,11 @@
       <c r="H2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -691,8 +719,11 @@
       <c r="H3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -717,8 +748,11 @@
       <c r="H4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -742,6 +776,23 @@
       </c>
       <c r="H5" t="s">
         <v>2</v>
+      </c>
+      <c r="I5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -757,6 +808,48 @@
     <ignoredError sqref="C2 C5 E2:H2 C3 E3:F3 C4 E4:F4 E5:F5 D1 H1" numberStoredAsText="1"/>
   </ignoredErrors>
   <drawing r:id="rId5"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{686DBDE1-8816-4579-9A96-971500BCDDBB}">
+          <x14:formula1>
+            <xm:f>Sheet1!$A$1:$A$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>I2:I24</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0DB826B-5DA4-4637-BE7D-4AE258B25B36}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
